--- a/backend/data/donglin/agent_demo/A1_freeform.xlsx
+++ b/backend/data/donglin/agent_demo/A1_freeform.xlsx
@@ -12569,12 +12569,12 @@
       </c>
       <c r="T124" s="4" t="inlineStr">
         <is>
-          <t>法人和非法人组织公共信用信息报告(V2.0)：甲公司（通风机械），统一社会信用代码 91320206MA1MDD2LXW，报告编号 2026030311540815052Q48，生成日期 2026-03-03，出具单位 国家公共信用和地理空间信息中心。信用概要：行政管理7条、诚实守信1条（纳税信用A级2022）、严重失信0、经营异常0、信用承诺0、信用评价0、司法判决0、其他0。属公共/行政信用信息，无银行存款余额数据。</t>
+          <t>法人和非法人组织公共信用信息报告(V2.0)：甲公司（通风机械），统一社会信用代码 91XXXXXXXXXXXXXXXX，报告编号 2026030311540815052Q48，生成日期 2026-03-03，出具单位 国家公共信用和地理空间信息中心。信用概要：行政管理7条、诚实守信1条（纳税信用A级2022）、严重失信0、经营异常0、信用承诺0、信用评价0、司法判决0、其他0。属公共/行政信用信息，无银行存款余额数据。</t>
         </is>
       </c>
       <c r="U124" s="4" t="inlineStr">
         <is>
-          <t>{"机构名称": "甲公司（通风机械）","统一社会信用代码": "91320206MA1MDD2LXW","报告编号": "2026030311540815052Q48","报告生成日期": "2026-03-03","出具单位": "国家公共信用和地理空间信息中心","法定代表人": "杨春平","企业类型": "有限责任公司(自然人投资或控股)","成立日期": "2015-12-28","住所": "无锡市惠山区堰桥街道堰锦路22","信用概要": {"行政管理": "7条","诚实守信": "1条","严重失信": "0条","经营异常": "0条","信用承诺": "0条","信用评价": "0条","司法判决": "0条","其他": "0条"},"纳税信用": "A级(评价年度2022，国家税务总局)","报告性质": "公共/行政信用信息，非银行征信，无货币资金余额数据","method": "pdf_text_layer (deterministic)","full_text": "                                     扫一扫\n\n\n\n\n                                     核验码\n\n\n\n\n   法人和非法人组织\n   公共信用信息报告\n            版本号V2.0\n\n\n\n机构名称：       甲公司（通风机械）\n\n统一社会信用代码：   91320206MA1MDD2LXW\n\n报告编号：       2026030311540815052Q48\n\n\n\n\n报告生成日期      2026年03月03日\n\n\n报告出具单位      国家公共信用和地理空间信息中心\n\f                                                                                           报告编号：2026030311540815052Q48\n                                                                                           生成时间：2026年03月03日 11:54:08\n\n-------------------------------------------------------------------------------------------------------------------------\n\n                                                                                                                扫一扫\n\n\n\n                                   公共信用信息概览\n                                                                                                                核验码\n\n\n\n甲公司（通风机械）                                                                                        存续      守信激励对象\n\n\n\n\n登记注册基本信息\n| 基础信息\n\n\n                                                               法定代表人/负责\n  统一社会信用代码                 91320206MA1MDD2LXW                  人/执行事务合伙               杨春平\n                                                               人\n\n\n  企业类型                     有限责任公司(自然人投资或控股)                    成立日期                   2015-12-28\n\n\n  住所                       无锡市惠山区堰桥街道堰锦路22\n\n\n\n| 海关注册登记信息\n\n\n  所在地海关                    无锡海关                                备案日期                   2017-12-25\n\n\n  经营类别                     ——                                  海关注销标志                 正常\n\n\n\n\n信用信息概要\n\n  行政管理                     7条                                  诚实守信                   1条\n\n\n  严重失信                     0条                                  经营异常                   0条\n\n\n  信用承诺                     0条                                  信用评价                   0条\n\n\n  司法判决                     0条                                  其他                     0条\n\n\n\n  报告生成日期                   2026年03月03日                         报告出具单位                 国家公共信用和地理空间信息中心\n\n\n\n\n                                                       第1页 共8页\n\f                                                                                           报告编号：2026030311540815052Q48\n                                                                                           生成时间：2026年03月03日 11:54:08\n\n-------------------------------------------------------------------------------------------------------------------------\n\n                                                                                                                扫一扫\n\n\n                                                报告说明\n                                                                                                                核验码\n\n\n\n\n       1.本报告所展示的数据和资料为公共信用信息，“信用中国”网站承诺在数据汇总、加工、整合的过\n\n       程中保持客观中立，不主动编辑或修改信息的内容。\n\n\n       2.受限于现有技术水平等原因，对此报告信息的展示，并不视为“信用中国”对其内容的真实性、准\n\n       确性、完整性、时效性作出任何形式的确认或担保。请在依据本报告信息作出判断或决策前，自行进\n\n       一步核实此类信息的完整或准确性，并自行承担使用后果。\n\n\n       3.如认为本报告所展示信息存在错误、遗漏、重复公示、不应公示、超期公示或与认定机关信息不一\n\n       致等情况，请以数据源单位的信息为准，并可按照网站“信用信息异议申诉指南”提出异议申诉；如\n\n       需对相关行政处罚信息进行信用修复，可按照网站“行政处罚信息信用修复流程指引”提出信用修复\n\n       申请；如需对相关严重失信主体名单进行信用修复，请咨询名单认定单位。\n\n\n       4.本报告已添加“信用中国”水印、生成唯一的报告编号和报告核验码。如需对内容的真实性进行核\n\n       验，可通过扫一扫报告首页“核验码”，查看本报告生成时的内容与纸质版报告内容是否一致。\n\n\n       5.本报告展示行政管理、诚实守信、严重失信、经营异常、信用承诺、信用评价、司法判决以及其他\n\n       类等信息，因篇幅有限，单类信息仅按更新程度展示最近日期的100条。如有特殊需求，请与我们联\n\n       系。\n\n\n\n\n                                                       第2页 共8页\n\f                                                                                           报告编号：2026030311540815052Q48\n                                                                                           生成时间：2026年03月03日 11:54:08\n\n-------------------------------------------------------------------------------------------------------------------------\n\n                                                                                                                扫一扫\n\n\n                                                      正文\n                                                                                                                核验码\n\n甲公司（通风机械）                                                                                       存续       守信激励对象\n\n\n\n\n一、登记注册基础信息\n\n\n     | 基础信息\n\n     企业名称：                          甲公司（通风机械）\n\n     统一社会信用代码：                      91320206MA1MDD2LXW\n\n     法定代表人/负责人/执行事务                 杨春平\n     合伙人：\n\n     企业类型：                          有限责任公司(自然人投资或控股)\n\n     成立日期：                          2015-12-28\n\n     住所：                            无锡市惠山区堰桥街道堰锦路22\n\n     | 海关注册登记信息\n\n     所在地海关：                         无锡海关\n\n     备案日期：                          2017-12-25\n\n     经营类别：                          ——\n\n     海关注销标志：                        正常\n\n\n\n\n二、行政管理信息 (共 7 条)\n\n\n     | 行政许可\n\n     行政许可决定文书号：                     (320202850604)登字﹝2024﹞第10210064号                                         第1条\n\n\n     行政许可决定文书名称：                    登字\n\n     许可证书名称：                        登字\n\n     许可类别：                          登记\n\n     许可编号：                          (320202850604)登字[2024]第10210064号\n\n\n\n\n                                                       第3页 共8页\n\f                                                                                           报告编号：2026030311540815052Q48\n                                                                                           生成时间：2026年03月03日 11:54:08\n\n-------------------------------------------------------------------------------------------------------------------------\n\n\n\n\n     许可决定日期：                        2024-10-21\n\n     有效期自：                          2015-12-28\n\n     有效期至：                          2099-12-31\n\n     许可内容：                          登字\n\n     许可机关：                          无锡市惠山区行政审批局\n\n     许可机关统一社会信用代码：                  11320206014007705X\n\n     数据来源单位：                        江苏省市场监督管理局\n\n     数据来源单位统一社会信用代                  11320000MB151840XJ\n     码：\n\n\n     --------------------------------------------             --------------------------------------------\n\n     | 行政许可\n\n     行政许可决定文书号：                     (320202850604)登字﹝2024﹞第09290187号                                         第2条\n\n\n     行政许可决定文书名称：                    登字\n\n     许可证书名称：                        登字\n\n     许可类别：                          登记\n\n     许可编号：                          (320202850604)登字[2024]第09290187号\n\n     许可决定日期：                        2024-09-29\n\n     有效期自：                          2015-12-28\n\n     有效期至：                          2099-12-31\n\n     许可内容：                          登字\n\n     许可机关：                          无锡市惠山区行政审批局\n\n     许可机关统一社会信用代码：                  11320206014007705X\n\n     数据来源单位：                        江苏省市场监督管理局\n\n     数据来源单位统一社会信用代                  11320000MB151840XJ\n     码：\n\n\n     --------------------------------------------             --------------------------------------------\n\n     | 行政许可\n\n     行政许可决定文书号：                     无行政许可决定文书号                                                               第3条\n\n\n\n\n                                                       第4页 共8页\n\f                                                                                           报告编号：2026030311540815052Q48\n                                                                                           生成时间：2026年03月03日 11:54:08\n\n-------------------------------------------------------------------------------------------------------------------------\n\n\n\n\n     行政许可决定文书名称：                    空\n\n     许可证书名称：                        特种设备使用登记证\n\n     许可类别：                          普通\n\n     许可编号：                          容15苏B21061(22)\n\n     许可决定日期：                        2022-11-11\n\n     有效期自：                          2022-11-11\n\n     有效期至：                          2099-12-31\n\n     许可内容：                          设备类别:第二类压力容器，产品名称:储气罐，出厂编号:FP2004D387-2，单位内编号\n                                    :R-01，设备代码:215033025202000259，设备注册代码:21503202062022110016\n\n     许可机关：                          无锡市惠山区市场监督管理局\n\n     许可机关统一社会信用代码：                  11320206014007705X\n\n     数据来源单位：                        无锡市发展改革研究中心\n\n     数据来源单位统一社会信用代                  12320200466284957C\n     码：\n\n\n     --------------------------------------------             --------------------------------------------\n\n     | 行政许可\n\n     行政许可决定文书号：                     ﹝02850909-7﹞公司变更﹝2021﹞第05240007号                                         第4条\n\n\n     行政许可决定文书名称：                    企业设立登记\n\n     许可证书名称：                        ——\n\n     许可类别：                          登记\n\n     许可编号：                          ——\n\n     许可决定日期：                        2021-05-24\n\n     有效期自：                          2021-05-24\n\n     有效期至：                          2099-12-31\n\n     许可内容：                          变更登记\n\n     许可机关：                          无锡市惠山区市场监督管理局\n\n     许可机关统一社会信用代码：                  11320206014007705X\n\n\n\n\n                                                       第5页 共8页\n\f                                                                                           报告编号：2026030311540815052Q48\n                                                                                           生成时间：2026年03月03日 11:54:08\n\n-------------------------------------------------------------------------------------------------------------------------\n\n\n\n\n     数据来源单位：                        无锡市发展改革研究中心\n\n     数据来源单位统一社会信用代                  12320200466284957C\n     码：\n\n\n     --------------------------------------------             --------------------------------------------\n\n     | 行政许可\n\n     行政许可决定文书号：                     (02850909-7)公司变更﹝2020﹞第09020026号                                         第5条\n\n\n     行政许可决定文书名称：                    公司变更\n\n     许可证书名称：                        公司变更\n\n     许可类别：                          登记\n\n     许可编号：                          (02850909-7)公司变更[2020]第09020026号\n\n     许可决定日期：                        2020-09-02\n\n     有效期自：                          2015-12-28\n\n     有效期至：                          2099-12-31\n\n     许可内容：                          公司变更\n\n     许可机关：                          无锡市惠山区市场监督管理局\n\n     许可机关统一社会信用代码：                  11320206014007705X\n\n     数据来源单位：                        江苏省市场监督管理局\n\n     数据来源单位统一社会信用代                  11320000MB151840XJ\n     码：\n\n\n     --------------------------------------------             --------------------------------------------\n\n     | 行政许可\n\n     行政许可决定书文号：                     (02851003)公司设立﹝2015﹞第12280003号                                           第6条\n\n\n     许可有效期：                         ——\n\n     许可决定日期：                        2015-12-28\n\n     许可截止日期：                        2099-12-31\n\n     许可内容：                          开业登记\n\n     许可机关：                          无锡市惠山区市场监督管理局\n\n     审核类型：                          登记\n     --------------------------------------------             --------------------------------------------\n\n\n                                                       第6页 共8页\n\f                                                                                           报告编号：2026030311540815052Q48\n                                                                                           生成时间：2026年03月03日 11:54:08\n\n-------------------------------------------------------------------------------------------------------------------------\n\n\n\n\n     | 行政许可\n\n     行政许可决定文书号：                     ﹝02850909-7﹞公司变更﹝2020﹞第12110005号                                         第7条\n\n\n     行政许可决定文书名称：                    公司变更\n\n     许可证书名称：                        公司变更\n\n     许可类别：                          登记\n\n     许可编号：                          (02850909-7)公司变更[2020]第12110005号\n\n     许可决定日期：                        2015-12-28\n\n     有效期自：                          2015-12-28\n\n     有效期至：                          2099-12-31\n\n     许可内容：                          公司变更\n\n     许可机关：                          无锡市惠山区市场监督管理局\n\n     许可机关统一社会信用代码：                  11320206014007705X\n\n     数据来源单位：                        江苏省市场监督管理局\n\n     数据来源单位统一社会信用代                  11320000MB151840XJ\n     码：\n\n\n\n\n三、诚实守信相关荣誉信息 (共 1 条)\n\n\n     | 纳税信用A级纳税人\n\n     纳税人名称：                         甲公司（通风机械）                                                             第1条\n\n\n     纳税人识别号：                        91320206MA1MDD2LXW\n\n     评价年度：                          2022\n\n     数据来源：                          国家税务总局\n\n\n\n\n四、严重失信信息 (共 0 条)\n\n\n                                                  查询期内无相关记录\n\n\n\n\n                                                       第7页 共8页\n\f                                                                                                                                                                                                                                                                                                                                             报告编号：2026030311540815052Q48\n                                                                                                                                                                                                                                                                                                                                             生成时间：2026年03月03日 11:54:08\n\n-------------------------------------------------------------------------------------------------------------------------\n\n\n\n五、经营（活动）异常名录（状态）信息 (共 0 条)\n\n\n                                                                                                                                                                                               查询期内无相关记录\n\n\n\n六、信用承诺信息 (共 0 条)\n\n\n                                                                                                                                                                                               查询期内无相关记录\n\n\n\n七、信用评价信息 (共 0 条)\n\n\n                                                                                                                                                                                 此项信息相关部门暂未提供\n\n\n\n八、司法判决及执行信息 (共 0 条)\n\n\n                                                                                                                                                                                 此项信息相关部门暂未提供\n\n\n\n九、其他信息 (共 0 条)\n\n\n                                                                                                                                                                                               查询期内无相关记录\n\n\n\n十、信用状况提升建议\n\n\n                    建议秉持诚信理念，合法有序开展经营活动。\n\n\n\n\n  ///////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////\n\n\n                                                                                                                                                                                                                            结束   ///////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////\n\n\n\n\n                                                                                                                                                                                                                   第8页 共8页\n\f","steward_version": "data-steward/A1-root-pdfs"}</t>
+          <t>{"机构名称": "甲公司（通风机械）","统一社会信用代码": "91XXXXXXXXXXXXXXXX","报告编号": "2026030311540815052Q48","报告生成日期": "2026-03-03","出具单位": "国家公共信用和地理空间信息中心","法定代表人": "杨春平","企业类型": "有限责任公司(自然人投资或控股)","成立日期": "2015-12-28","住所": "无锡市惠山区堰桥街道堰锦路22","信用概要": {"行政管理": "7条","诚实守信": "1条","严重失信": "0条","经营异常": "0条","信用承诺": "0条","信用评价": "0条","司法判决": "0条","其他": "0条"},"纳税信用": "A级(评价年度2022，国家税务总局)","报告性质": "公共/行政信用信息，非银行征信，无货币资金余额数据","method": "pdf_text_layer (deterministic)","full_text": "                                     扫一扫\n\n\n\n\n                                     核验码\n\n\n\n\n   法人和非法人组织\n   公共信用信息报告\n            版本号V2.0\n\n\n\n机构名称：       甲公司（通风机械）\n\n统一社会信用代码：   91XXXXXXXXXXXXXXXX\n\n报告编号：       2026030311540815052Q48\n\n\n\n\n报告生成日期      2026年03月03日\n\n\n报告出具单位      国家公共信用和地理空间信息中心\n\f                                                                                           报告编号：2026030311540815052Q48\n                                                                                           生成时间：2026年03月03日 11:54:08\n\n-------------------------------------------------------------------------------------------------------------------------\n\n                                                                                                                扫一扫\n\n\n\n                                   公共信用信息概览\n                                                                                                                核验码\n\n\n\n甲公司（通风机械）                                                                                        存续      守信激励对象\n\n\n\n\n登记注册基本信息\n| 基础信息\n\n\n                                                               法定代表人/负责\n  统一社会信用代码                 91XXXXXXXXXXXXXXXX                  人/执行事务合伙               杨春平\n                                                               人\n\n\n  企业类型                     有限责任公司(自然人投资或控股)                    成立日期                   2015-12-28\n\n\n  住所                       无锡市惠山区堰桥街道堰锦路22\n\n\n\n| 海关注册登记信息\n\n\n  所在地海关                    无锡海关                                备案日期                   2017-12-25\n\n\n  经营类别                     ——                                  海关注销标志                 正常\n\n\n\n\n信用信息概要\n\n  行政管理                     7条                                  诚实守信                   1条\n\n\n  严重失信                     0条                                  经营异常                   0条\n\n\n  信用承诺                     0条                                  信用评价                   0条\n\n\n  司法判决                     0条                                  其他                     0条\n\n\n\n  报告生成日期                   2026年03月03日                         报告出具单位                 国家公共信用和地理空间信息中心\n\n\n\n\n                                                       第1页 共8页\n\f                                                                                           报告编号：2026030311540815052Q48\n                                                                                           生成时间：2026年03月03日 11:54:08\n\n-------------------------------------------------------------------------------------------------------------------------\n\n                                                                                                                扫一扫\n\n\n                                                报告说明\n                                                                                                                核验码\n\n\n\n\n       1.本报告所展示的数据和资料为公共信用信息，“信用中国”网站承诺在数据汇总、加工、整合的过\n\n       程中保持客观中立，不主动编辑或修改信息的内容。\n\n\n       2.受限于现有技术水平等原因，对此报告信息的展示，并不视为“信用中国”对其内容的真实性、准\n\n       确性、完整性、时效性作出任何形式的确认或担保。请在依据本报告信息作出判断或决策前，自行进\n\n       一步核实此类信息的完整或准确性，并自行承担使用后果。\n\n\n       3.如认为本报告所展示信息存在错误、遗漏、重复公示、不应公示、超期公示或与认定机关信息不一\n\n       致等情况，请以数据源单位的信息为准，并可按照网站“信用信息异议申诉指南”提出异议申诉；如\n\n       需对相关行政处罚信息进行信用修复，可按照网站“行政处罚信息信用修复流程指引”提出信用修复\n\n       申请；如需对相关严重失信主体名单进行信用修复，请咨询名单认定单位。\n\n\n       4.本报告已添加“信用中国”水印、生成唯一的报告编号和报告核验码。如需对内容的真实性进行核\n\n       验，可通过扫一扫报告首页“核验码”，查看本报告生成时的内容与纸质版报告内容是否一致。\n\n\n       5.本报告展示行政管理、诚实守信、严重失信、经营异常、信用承诺、信用评价、司法判决以及其他\n\n       类等信息，因篇幅有限，单类信息仅按更新程度展示最近日期的100条。如有特殊需求，请与我们联\n\n       系。\n\n\n\n\n                                                       第2页 共8页\n\f                                                                                           报告编号：2026030311540815052Q48\n                                                                                           生成时间：2026年03月03日 11:54:08\n\n-------------------------------------------------------------------------------------------------------------------------\n\n                                                                                                                扫一扫\n\n\n                                                      正文\n                                                                                                                核验码\n\n甲公司（通风机械）                                                                                       存续       守信激励对象\n\n\n\n\n一、登记注册基础信息\n\n\n     | 基础信息\n\n     企业名称：                          甲公司（通风机械）\n\n     统一社会信用代码：                      91XXXXXXXXXXXXXXXX\n\n     法定代表人/负责人/执行事务                 杨春平\n     合伙人：\n\n     企业类型：                          有限责任公司(自然人投资或控股)\n\n     成立日期：                          2015-12-28\n\n     住所：                            无锡市惠山区堰桥街道堰锦路22\n\n     | 海关注册登记信息\n\n     所在地海关：                         无锡海关\n\n     备案日期：                          2017-12-25\n\n     经营类别：                          ——\n\n     海关注销标志：                        正常\n\n\n\n\n二、行政管理信息 (共 7 条)\n\n\n     | 行政许可\n\n     行政许可决定文书号：                     (320202850604)登字﹝2024﹞第10210064号                                         第1条\n\n\n     行政许可决定文书名称：                    登字\n\n     许可证书名称：                        登字\n\n     许可类别：                          登记\n\n     许可编号：                          (320202850604)登字[2024]第10210064号\n\n\n\n\n                                                       第3页 共8页\n\f                                                                                           报告编号：2026030311540815052Q48\n                                                                                           生成时间：2026年03月03日 11:54:08\n\n-------------------------------------------------------------------------------------------------------------------------\n\n\n\n\n     许可决定日期：                        2024-10-21\n\n     有效期自：                          2015-12-28\n\n     有效期至：                          2099-12-31\n\n     许可内容：                          登字\n\n     许可机关：                          无锡市惠山区行政审批局\n\n     许可机关统一社会信用代码：                  11320206014007705X\n\n     数据来源单位：                        江苏省市场监督管理局\n\n     数据来源单位统一社会信用代                  11320000MB151840XJ\n     码：\n\n\n     --------------------------------------------             --------------------------------------------\n\n     | 行政许可\n\n     行政许可决定文书号：                     (320202850604)登字﹝2024﹞第09290187号                                         第2条\n\n\n     行政许可决定文书名称：                    登字\n\n     许可证书名称：                        登字\n\n     许可类别：                          登记\n\n     许可编号：                          (320202850604)登字[2024]第09290187号\n\n     许可决定日期：                        2024-09-29\n\n     有效期自：                          2015-12-28\n\n     有效期至：                          2099-12-31\n\n     许可内容：                          登字\n\n     许可机关：                          无锡市惠山区行政审批局\n\n     许可机关统一社会信用代码：                  11320206014007705X\n\n     数据来源单位：                        江苏省市场监督管理局\n\n     数据来源单位统一社会信用代                  11320000MB151840XJ\n     码：\n\n\n     --------------------------------------------             --------------------------------------------\n\n     | 行政许可\n\n     行政许可决定文书号：                     无行政许可决定文书号                                                               第3条\n\n\n\n\n                                                       第4页 共8页\n\f                                                                                           报告编号：2026030311540815052Q48\n                                                                                           生成时间：2026年03月03日 11:54:08\n\n-------------------------------------------------------------------------------------------------------------------------\n\n\n\n\n     行政许可决定文书名称：                    空\n\n     许可证书名称：                        特种设备使用登记证\n\n     许可类别：                          普通\n\n     许可编号：                          容15苏B21061(22)\n\n     许可决定日期：                        2022-11-11\n\n     有效期自：                          2022-11-11\n\n     有效期至：                          2099-12-31\n\n     许可内容：                          设备类别:第二类压力容器，产品名称:储气罐，出厂编号:FP2004D387-2，单位内编号\n                                    :R-01，设备代码:215033025202000259，设备注册代码:21503202062022110016\n\n     许可机关：                          无锡市惠山区市场监督管理局\n\n     许可机关统一社会信用代码：                  11320206014007705X\n\n     数据来源单位：                        无锡市发展改革研究中心\n\n     数据来源单位统一社会信用代                  12320200466284957C\n     码：\n\n\n     --------------------------------------------             --------------------------------------------\n\n     | 行政许可\n\n     行政许可决定文书号：                     ﹝02850909-7﹞公司变更﹝2021﹞第05240007号                                         第4条\n\n\n     行政许可决定文书名称：                    企业设立登记\n\n     许可证书名称：                        ——\n\n     许可类别：                          登记\n\n     许可编号：                          ——\n\n     许可决定日期：                        2021-05-24\n\n     有效期自：                          2021-05-24\n\n     有效期至：                          2099-12-31\n\n     许可内容：                          变更登记\n\n     许可机关：                          无锡市惠山区市场监督管理局\n\n     许可机关统一社会信用代码：                  11320206014007705X\n\n\n\n\n                                                       第5页 共8页\n\f                                                                                           报告编号：2026030311540815052Q48\n                                                                                           生成时间：2026年03月03日 11:54:08\n\n-------------------------------------------------------------------------------------------------------------------------\n\n\n\n\n     数据来源单位：                        无锡市发展改革研究中心\n\n     数据来源单位统一社会信用代                  12320200466284957C\n     码：\n\n\n     --------------------------------------------             --------------------------------------------\n\n     | 行政许可\n\n     行政许可决定文书号：                     (02850909-7)公司变更﹝2020﹞第09020026号                                         第5条\n\n\n     行政许可决定文书名称：                    公司变更\n\n     许可证书名称：                        公司变更\n\n     许可类别：                          登记\n\n     许可编号：                          (02850909-7)公司变更[2020]第09020026号\n\n     许可决定日期：                        2020-09-02\n\n     有效期自：                          2015-12-28\n\n     有效期至：                          2099-12-31\n\n     许可内容：                          公司变更\n\n     许可机关：                          无锡市惠山区市场监督管理局\n\n     许可机关统一社会信用代码：                  11320206014007705X\n\n     数据来源单位：                        江苏省市场监督管理局\n\n     数据来源单位统一社会信用代                  11320000MB151840XJ\n     码：\n\n\n     --------------------------------------------             --------------------------------------------\n\n     | 行政许可\n\n     行政许可决定书文号：                     (02851003)公司设立﹝2015﹞第12280003号                                           第6条\n\n\n     许可有效期：                         ——\n\n     许可决定日期：                        2015-12-28\n\n     许可截止日期：                        2099-12-31\n\n     许可内容：                          开业登记\n\n     许可机关：                          无锡市惠山区市场监督管理局\n\n     审核类型：                          登记\n     --------------------------------------------             --------------------------------------------\n\n\n                                                       第6页 共8页\n\f                                                                                           报告编号：2026030311540815052Q48\n                                                                                           生成时间：2026年03月03日 11:54:08\n\n-------------------------------------------------------------------------------------------------------------------------\n\n\n\n\n     | 行政许可\n\n     行政许可决定文书号：                     ﹝02850909-7﹞公司变更﹝2020﹞第12110005号                                         第7条\n\n\n     行政许可决定文书名称：                    公司变更\n\n     许可证书名称：                        公司变更\n\n     许可类别：                          登记\n\n     许可编号：                          (02850909-7)公司变更[2020]第12110005号\n\n     许可决定日期：                        2015-12-28\n\n     有效期自：                          2015-12-28\n\n     有效期至：                          2099-12-31\n\n     许可内容：                          公司变更\n\n     许可机关：                          无锡市惠山区市场监督管理局\n\n     许可机关统一社会信用代码：                  11320206014007705X\n\n     数据来源单位：                        江苏省市场监督管理局\n\n     数据来源单位统一社会信用代                  11320000MB151840XJ\n     码：\n\n\n\n\n三、诚实守信相关荣誉信息 (共 1 条)\n\n\n     | 纳税信用A级纳税人\n\n     纳税人名称：                         甲公司（通风机械）                                                             第1条\n\n\n     纳税人识别号：                        91XXXXXXXXXXXXXXXX\n\n     评价年度：                          2022\n\n     数据来源：                          国家税务总局\n\n\n\n\n四、严重失信信息 (共 0 条)\n\n\n                                                  查询期内无相关记录\n\n\n\n\n                                                       第7页 共8页\n\f                                                                                                                                                                                                                                                                                                                                             报告编号：2026030311540815052Q48\n                                                                                                                                                                                                                                                                                                                                             生成时间：2026年03月03日 11:54:08\n\n-------------------------------------------------------------------------------------------------------------------------\n\n\n\n五、经营（活动）异常名录（状态）信息 (共 0 条)\n\n\n                                                                                                                                                                                               查询期内无相关记录\n\n\n\n六、信用承诺信息 (共 0 条)\n\n\n                                                                                                                                                                                               查询期内无相关记录\n\n\n\n七、信用评价信息 (共 0 条)\n\n\n                                                                                                                                                                                 此项信息相关部门暂未提供\n\n\n\n八、司法判决及执行信息 (共 0 条)\n\n\n                                                                                                                                                                                 此项信息相关部门暂未提供\n\n\n\n九、其他信息 (共 0 条)\n\n\n                                                                                                                                                                                               查询期内无相关记录\n\n\n\n十、信用状况提升建议\n\n\n                    建议秉持诚信理念，合法有序开展经营活动。\n\n\n\n\n  ///////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////\n\n\n                                                                                                                                                                                                                            结束   ///////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////////\n\n\n\n\n                                                                                                                                                                                                                   第8页 共8页\n\f","steward_version": "data-steward/A1-root-pdfs"}</t>
         </is>
       </c>
       <c r="V124" s="4" t="inlineStr"/>
@@ -12653,12 +12653,12 @@
       </c>
       <c r="T125" s="4" t="inlineStr">
         <is>
-          <t>中国人民银行征信中心 企业信用报告(自主查询版)：甲公司（通风机械），中征码 3202060003004372，统一社会信用代码 91320206MA1MDD2LXW，查询机构 中国农业银行股份有限公司江苏省分行，报告时间 2026-05-25T15:02:46，共32页。信息概要：借贷交易余额1240万元、担保交易余额180万元，被追偿/关注/不良均为0；未结清短期借款5户1240万元，银行承兑汇票14户180万元。</t>
+          <t>中国人民银行征信中心 企业信用报告(自主查询版)：甲公司（通风机械），中征码 3202060003004372，统一社会信用代码 91XXXXXXXXXXXXXXXX，查询机构 中国农业银行股份有限公司江苏省分行，报告时间 2026-05-25T15:02:46，共32页。信息概要：借贷交易余额1240万元、担保交易余额180万元，被追偿/关注/不良均为0；未结清短期借款5户1240万元，银行承兑汇票14户180万元。</t>
         </is>
       </c>
       <c r="U125" s="4" t="inlineStr">
         <is>
-          <t>{"企业名称": "甲公司（通风机械）","中征码": "3202060003004372","统一社会信用代码": "91320206MA1MDD2LXW","查询机构": "中国农业银行股份有限公司江苏省分行","报告时间": "2026-05-25T15:02:46","报告编号": "NO.2026052515024689189187","页数": 32,"汇率_美元折人民币": "6.86","单位说明": "金额类数据项单位均为万元","method": "pdf_text_layer (deterministic)","full_text": "                          NO.2026052515024689189187\n\n\n\n\n        企业信用报告\n        （自主查询版）\n\n\n\n\n企业名称：         甲公司（通风机械）\n\n中征码：         3202060003004372\n\n统一社会信用代码： 91320206MA1MDD2LXW\n\n查询机构：        中国农业银行股份有限公司江苏省分行\n\n报告时间：        2026-05-25T15:02:46\n\n\n\n\n           第 1 页/共 32 页\n\f                         报告说明\n1．本报告由中国人民银行征信中心出具，依据截止报告时间征信系统记录的信息生成。除征信中心标注外，信息均由相关数据提\n供机构和信息主体提供，征信中心不保证其真实性和准确性，但承诺在信息汇总、加工、整合的全过程中保持客观、中立的地\n位。\n2．本报告所展示的基本信息来自征信系统对不同数据来源提供的同一个信息主体基本信息进行整合后的结果。\n3．本报告中信贷交易包括借贷交易和担保交易。\n4．本报告中借贷交易包括各种形式的贷款，也包括以各种其他名义融资但实质上是借贷的行为，即融资方负有明确还款责任的交\n易。常见的产品种类包括：贷款、贸易融资、票据贴现、保理、透支、融资租赁、回购、垫款、黄金证券借贷、公司信用债等。\n5．本报告中担保交易指第三人和债权人约定，当债务人不履行债务时，第三人按约定履行债务的行为。包括名义上没有担保合同\n约定但当债务人违约时、第三人实质上要代偿的行为。常见的产品种类包括：银行承兑汇票、信用证、银行保函、融资担保公司\n提供的担保服务，保险公司提供的信用保证保险服务。\n6．本报告中被追偿业务是指剩余本息处于催收状态（即债权人要求债务人尽快归还全部借款）的借贷交易。常见的产品种类包\n括：由资产管理公司处置的债务、垫款（含担保代偿）。\n7．本报告中的短期借款、中长期借款是指借贷交易中除被追偿业务、循环透支、贴现之外的业务，按照 “借款期限分类”划\n分，分别对应其中的短期、中期和长期。\n8．本报告中借贷交易的正常类是指除被追偿业务之外，五级分类为正常或者五级分类为“未分类”且逾期天数为0的业务；关注\n类是指除被追偿业务之外，五级分类为关注或者五级分类为“未分类”且逾期0至90天的业务；不良类是指除被追偿业务之外，五\n级分类为“次级”、“可疑”、“损失”、“违约”或者五级分类为“未分类”且逾期90天以上的业务。\n9．本报告中担保交易的正常类、关注类、不良类分别对应五级分类为正常、关注和后三类的业务。\n10．本报告中信息概要部分中的负债历史信息，其中负债是指由信贷交易所产生的债务；逾期总额、逾期本金是指除被追偿业务\n之外的借贷交易的逾期总额（含欠息）合计及逾期本金合计。\n11．本报告仅展示一定期限范围内的已结清信贷信息、非信贷信息、公共信息。\n12．如无特别说明，本报告中的金额类数据项单位均为万元。\n13．如无特别说明，本报告中的金额类汇总数据项均为人民币计价。外币折人民币的计算依据国家外汇管理局当月公布的各种货\n币对美元折算率表。\n14．如信息记录斜体展示，则说明信息主体对此条记录存在异议。\n15．数据提供机构说明是报数机构对报告中的信息记录或对信息主体所作的补充说明。\n16．征信中心说明是征信中心对报告中的信息记录或对信息主体所作的说明。\n17．信息主体声明是信息主体对报数机构提供的信息记录所作的简要说明。\n18．信息主体有权对本报告中的内容提出异议。如有异议，可联系报数机构，也可到当地信用报告查询网点（具体地址可查询征\n信中心网站www.pbccrc.org.cn）提出异议申请。\n19．本报告仅向信息主体提供，不为金融机构授信管理目的使用，请妥善保管。因保管不当造成信息泄露的，征信中心不承担相\n关责任。\n20．更多咨询，请致电全国客户服务热线400-810-8866。\n汇率（美元折人民币）：6.86        有效期：2026-05\n\n\n\n\n                          第 2 页/共 32 页\n\f                                                    身份标识\n\n           企业名称                        甲公司（通风机械）\n\n            中征码                        3202060003004372\n\n      统一社会信用代码                         91320206MA1MDD2LXW\n\n       组织机构代码                          MA1MDD2LX\n\n           工商注册号                       91320206MA1MDD2LXW\n\n     纳税人识别号（国税）                        91320206MA1MDD2LXW\n\n     纳税人识别号（地税）                        91320206MA1MDD2LXW\n\n\n\n\n                                                    信息概要\n\n                                                                       当前有未结清信贷                     首次有相关还款\n 首次有信贷交易的年份                    发生信贷交易的机构数                               交易的机构数                       责任的年份\n\n           2019                             10                               5                           2022\n\n\n\n                        借贷交易                                                               担保交易\n\n余额                                                    1240        余额                                                      180\n\n其中：被追偿余额                                                  0       其中：关注类余额                                                 0\n\n     关注类余额                                                0            不良类余额                                               0\n\n     不良类余额                                                0\n\n\n\n 非信贷交易账户数                欠税记录条数                    民事判决记录条数                      强制执行记录条数            行政处罚记录条数\n\n       0                           0                          0                        0                        0\n\n\n\n 未结清信贷及授信信息概要\n                       正常类                        关注类                            不良类                      合计\n\n              账户数            余额             账户数           余额            账户数            余额           账户数             余额\n\n短期借款              5          1240             0               0          0                 0         5              1240\n\n 合计               5          1240             0               0          0                 0         5              1240\n\n\n\n                       正常类                        关注类                            不良类                      合计\n\n              账户数            余额             账户数           余额            账户数            余额           账户数             余额\n\n银行承兑汇             14         180              0               0          0                 0        14              180\n  票\n\n 合计               14         180              0               0          0                 0        14              180\n\n\n\n 相关还款责任信息概要\n                                       被追偿业务                                           其他借贷交易\n     责任类型\n                        还款责任                                      还款责任                              关注类余            不良类余\n                                        账户数        余额                        账户数               余额\n                         金额                                        金额                                 额              额\n\n\n                                                     第 3 页/共 32 页\n\f     个人信贷交易共同     --           0          0         --        1        17.30      0          0\n     还款人/共同债务人\n\n        合计        0            0          0         0         1        17.30      0          0\n\n\n\n     已结清信贷信息概要\n                  正常类账户数                  关注类账户数              不良类账户数                   合计\n\n      中长期借款             4                      0                   0                   4\n\n       短期借款             17                     0                   0                   17\n\n        合计              21                     0                   0                   21\n\n\n\n                  正常类账户数                  关注类账户数              不良类账户数                   合计\n\n      银行承兑汇票            181                    0                   0                   181\n\n        合计              181                    0                   0                   181\n\n\n\n\n                                          基本信息\n\n     基本概况信息\n                                                                          中国农业银行股份有限公司无\n        经济类型                  有限责任(公司)                   信息来源机构                锡分行\n\n                                                                          中国农业银行股份有限公司无\n       组织机构类型                      企业                    信息来源机构                锡分行\n\n                                                                          中国农业银行股份有限公司无\n        企业规模                   小型企业                      信息来源机构                锡分行\n\n                                                                          中国农业银行股份有限公司无\n        所属行业                 风机、风扇制造                     信息来源机构                锡分行\n\n                                                                          中国农业银行股份有限公司无\n        成立年份                       2015                  信息来源机构                锡分行\n\n                                                                          中国农业银行股份有限公司无\n     登记证书有效截止日期                    长期                    信息来源机构                锡分行\n\n                       无锡市惠山区堰桥街道堰锦路                                      中国农业银行股份有限公司无\n        登记地址                                             信息来源机构\n                             22                                                锡分行\n\n                       无锡市惠山区堰桥街道堰锦路                                      南京银行股份有限公司无锡城\n       办公/经营地址                                           信息来源机构\n                             22                                                北支行\n\n                                                                          中国农业银行股份有限公司无\n        存续状态                   正常营业                      信息来源机构                锡分行\n--\n\n\n\n     注册资本及主要出资人信息                                                       注册资本折人民币合计 1000万元\n\n        类型             出资方                身份标识类型              身份标识号码                  出资比例\n\n        股东             杨春平                    身份证          320125197904075814         51%\n\n        股东             黄燕红                    身份证          32028319890903322X         49%\n\n 信息来源机构：中国农业银行股份有限公司无锡分行                                                        更新日期：2026-01-30\n\n\n\n     主要组成人员信息\n\n\n\n                                          第 4 页/共 32 页\n\f         职位                  姓名                            证件类型                    证件号码\n\n法定代表人/非法人组织负责                杨春平                           身份证              320125197904075814\n      人\n\n信息来源机构：江苏银行股份有限公司无锡科技支行                                                        更新日期：2025-04-28\n\n\n\n 实际控制人\n              名称                           身份标识类型                          身份标识号码\n\n           杨春平                               身份证                        320125197904075814\n\n信息来源机构：中国农业银行股份有限公司无锡分行                                                        更新日期：2026-01-30\n\n\n\n\n                                   信贷记录明细\n\n 未结清信贷\n 短期借款                                                                                           共5笔\n           授信机构       业务种类         开立日期             到期日           币种       借款金额            发放形式\n\n                                                                                         最近一次还款\n账户编        担保方式        余额          五级分类            逾期总额          逾期本金      逾期月数            日期\n 号\n                     最近一次还款                       授信协议编\n         最近一次还款总额              特定交易提示                            历史表现             信息报告日期\n                       形式                           号\n\nD10023   南京银行股份有限    流动资金贷款       2025-11-21      2026-11-19     人民币元        440          无还本续贷\n010H00   公司无锡城北支行\n010413\n251121        保证       440          正常                0            0          0           2026-05-20\n000000\n  10          0.88    正常还款            --              --          见附件              2026-05-20\n\n         中国农业银行股份\nB10211               流动资金贷款       2025-12-25      2026-12-15     人民币元        300          无还本续贷\n         有限公司无锡分行\n000H00\n013201        保证       300          正常                0            0          0           2026-05-21\n202501\n 35943\n              0.60    正常还款            --              --          见附件              2026-05-21\n\n         交通银行股份有限    流动资金贷款       2025-07-31      2026-07-30     人民币元        200                新增\n          公司无锡分行\nB10512\n900H00        保证       200          正常                0            0          0           2026-05-21\n013222\n025100                                           B10512900H\n051554                                           0001BL1563\n              0.44    正常还款            --                          见附件              2026-05-21\n                                                 22250703944\n                                                      3\n\n         中国农业银行股份\nB10211               流动资金贷款       2025-12-25      2026-12-15     人民币元        200          无还本续贷\n         有限公司无锡分行\n000H00\n013201        保证       200          正常                0            0          0           2026-05-21\n202501\n 35927\n              0.40    正常还款            --              --          见附件              2026-05-21\n\n         江苏银行股份有限    流动资金贷款       2025-05-27      2026-05-26     人民币元        100                新增\n         公司无锡科技支行\nD10123\n010H00        保证       100          正常                0            0          0           2026-05-21\n01XW2\n505270\n000004                                           D10123010H\n  07                                             0001BC2025\n              0.23    正常还款            --                          见附件              2026-05-21\n                                                 0522001197\n                                                     DK\n\n\n\n\n                                           第 5 页/共 32 页\n\f 银行承兑汇票和信用证                                                                                  共 14 笔\n     授信机构                     业务种类         五级分类                     账户数                余额\n\n交通银行股份有限公司               银行承兑汇票              正常                          14            180\n\n\n\n  已结清信贷\n 中长期借款                                                                                        共4笔\n                 授信机构            业务种类      开立日期              到期日                 币种    借款金额\n  账户编号\n                 关闭日期            五级分类       最后一次还款日期                 最后一次还款形式          历史表现\n\n                 丰田汽车金融\n                （中国）有限公          其他贷款      2019-12-16       2021-12-16          人民币元     8.50\nY10041000H00        司\n01EHP2079494\n                 2021-12-16          正常        2021-12-16                     正常还款      见附件\n\n                梅赛德斯-奔驰\n                汽车金融有限公         固定资产贷款     2020-04-24       2021-10-24          人民币元     14.82\nY10061000H00       司\n01EIP1537196\n                 2021-10-22          正常        2021-10-22                     正常还款      见附件\n\n                平安国际融资租\nM10251100H0     赁（天津）有限          其他贷款      2020-05-25       2021-10-25          人民币元     20.25\n002HX2020PA        公司\nZL200008308-\n   ZL-01\n                 2021-08-16          正常        2021-08-16                     正常还款      见附件\n\n                平安国际融资租\nM10251100H0     赁（天津）有限          其他贷款      2020-05-15       2021-10-15          人民币元     19.80\n002HX2020PA        公司\nZL200008312-\n   ZL-01\n                 2021-08-16          正常        2021-08-16                     正常还款      见附件\n\n\n\n 短期借款                                                                                        共 17 笔\n                 授信机构            业务种类      开立日期              到期日                 币种    借款金额\n  账户编号\n                 关闭日期            五级分类       最后一次还款日期                 最后一次还款形式          历史表现\n\n                中国农业银行股\nB10211000H00    份有限公司无锡         流动资金贷款     2025-08-06       2026-08-04          人民币元         300\n0132012025008      分行\n     6673\n                 2025-12-25          正常        2025-12-25                     正常还款      见附件\n\n                中国农业银行股\nB10211000H00    份有限公司无锡         流动资金贷款     2025-08-08       2026-08-03          人民币元         200\n0132012025008      分行\n     7282\n                 2025-12-25          正常        2025-12-25                     正常还款      见附件\n\n                南京银行股份有\nD10023010H00    限公司无锡城北         流动资金贷款     2024-12-10       2025-12-08          人民币元         440\n0104132412100      支行\n   0000005\n                 2025-11-21          正常        2025-11-21                     正常还款      见附件\n\n                中国农业银行股\nB10211000H00    份有限公司无锡         流动资金贷款     2024-08-20       2025-08-19          人民币元         200\n0132012024009      分行\n     3062\n                 2025-08-08          正常        2025-08-08                     正常还款      见附件\n\n                中国农业银行股\nB10211000H00    份有限公司无锡         流动资金贷款     2024-08-20       2025-08-18          人民币元         300\n0132012024009      分行\n     2579\n                 2025-08-06          正常        2025-08-06                     正常还款      见附件\n\n\n\n\n                                          第 6 页/共 32 页\n\f                交通银行股份有\nB10512900H00                  流动资金贷款        2024-08-13       2025-08-12     人民币元    300\n                限公司无锡分行\n0132220240000\n    70638\n                 2025-07-31     正常              2025-07-31                正常还款     见附件\n\n                交通银行股份有\nB10512900H00                  流动资金贷款        2024-08-08       2025-08-07     人民币元    200\n                限公司无锡分行\n0132220240000\n    70095\n                 2025-07-31     正常              2025-07-31                正常还款     见附件\n\n                中国农业银行股\nB10211000H00    份有限公司无锡       流动资金贷款        2023-09-21       2024-09-20     人民币元    200\n0132012023010      分行\n     5691\n                 2024-08-20     正常              2024-08-20                正常还款     见附件\n\n                中国农业银行股\nB10211000H00    份有限公司无锡       流动资金贷款        2023-09-20       2024-09-18     人民币元    300\n0132012023010      分行\n     4308\n                 2024-08-19     正常              2024-08-19                正常还款     见附件\n\n                交通银行股份有\nB10512900H00                  流动资金贷款        2023-08-31       2024-08-31     人民币元    300\n                限公司无锡分行\n0132220230000\n    34697\n                 2024-08-12     正常              2024-08-12                正常还款     见附件\n\n                交通银行股份有\nB10512900H00                  流动资金贷款        2023-08-31       2024-08-31     人民币元    200\n                限公司无锡分行\n0132220230000\n    34729\n                 2024-08-05     正常              2024-08-05                正常还款     见附件\n\n                中国农业银行股\nB10211000H00    份有限公司无锡       流动资金贷款        2022-09-23       2023-09-22     人民币元    500\n0132012022007      分行\n     4966\n                 2023-09-21     正常              2023-09-21                正常还款     见附件\n\n                中国农业银行股\nB10211000H00    份有限公司无锡       流动资金贷款        2021-11-10       2022-11-09     人民币元    200\n0132012021008      分行\n     5887\n                 2022-09-23     正常              2022-09-23                正常还款     见附件\n\n                中国农业银行股\nB10211000H00    份有限公司无锡       流动资金贷款        2021-11-12       2022-11-11     人民币元    300\n0132012021008      分行\n     6662\n                 2022-09-23     正常              2022-09-23                正常还款     见附件\n\n                中国农业银行股\nB10211000H00    份有限公司无锡       流动资金贷款        2021-03-02       2022-03-01     人民币元    300\n0132012021001      分行\n     5429\n                 2021-11-12     正常              2021-11-12                正常还款     见附件\n\n                中国农业银行股\nB10211000H00    份有限公司无锡       流动资金贷款        2021-03-01       2022-02-21     人民币元    200\n0132012021001      分行\n     4919\n                 2021-11-10     正常              2021-11-10                正常还款     见附件\n\n                中国农业银行股\nB10211000H00    份有限公司无锡       流动资金贷款        2020-03-23       2021-03-12     人民币元    300\n0132012020001     惠山支行\n     7424\n                 2021-03-02     正常              2021-03-02                正常还款     见附件\n\n\n\n 银行承兑汇票和信用证                                                                        共 181 笔\n         授信机构                        业务种类                    五级分类          账户数     垫款标志\n\n    浙商银行股份有限公司                   银行承兑汇票                       正常            107     否\n\n    江苏银行股份有限公司                   银行承兑汇票                       正常            34      否\n\n江苏常熟农村商业银行股份有限                   银行承兑汇票                       正常            21      否\n      公司\n\n\n                                        第 7 页/共 32 页\n\f   交通银行股份有限公司                 银行承兑汇票                        正常                12               否\n\n  中国农业银行股份有限公司                银行承兑汇票                        正常                7                否\n\n\n\n 相关还款责任\n 为其他借款人承担的相关还款责任\n除贴现外的其他业务                                                                                       共1笔\n                    保证合同             还款责任       授信机构/                 开立日期/\n           责任类型              币种                              业务种类                   到期日         币种\n                     编号               金额        债权机构                  接收日期\n账户编号\n           借款金额/                                            逾期月数/     剩余还款\n                     余额     五级分类     逾期总额       逾期本金                                  信息报告日期\n           信用额度                                             还款状态       月数\n\nD1005584   个人信贷                                 深圳前海\n0H0001D    交易共同                                 微众银行         个人汽车     2025-02-     2030-02-\n                     --     人民币元        --                                                     人民币元\n18300640   还款人/共                                股份有限         消费贷款        10           10\n10926946   同债务人                                  公司\n72123250\n21002649\n  86440     22.42   17.30    正常         0          0              N      --            2026-05-10\n\n\n\n\n                                    公共记录明细\n\n 获得许可记录\n    许可部门            许可类型           许可日期                 截止日期                       许可内容\n\n无锡市惠山区行政             登记            2024-10-21           2099-12-31                  登字\n   审批局\n\n无锡市惠山区行政             登记            2024-09-29           2099-12-31                  登字\n   审批局\n\n                                                                      设备类别:第二类压力容器，产品名\n                                                                      称:储气罐，出厂编号:FP2004D387-\n无锡市惠山区市场             普通            2022-11-11           2099-12-31     2，单位内编号:R-01，设备代码\n  监督管理局                                                               :215033025202000259，设备注册\n                                                                        代码:21503202062022110016\n\n无锡市惠山区市场             登记            2021-05-24           2099-12-31                 变更登记\n  监督管理局\n\n无锡市惠山区市场             登记            2015-12-28           2099-12-31                 公司变更\n  监督管理局\n\n\n\n 获得认证记录\n           认证部门                   认证类型                    认证日期          截止日期                  认证内容\n\n                                                                                        2022年度纳税信\n       国家税务总局                纳税信用A级纳税人                       --        2028-12-31        用A级纳税人\n\n\n\n\n                                         第 8 页/共 32 页\n\f附件1：信用记录补充信息\n\n一、信贷记录\n（一）中长期借款的历史表现\n1.已结清账户编号                     授信机构：丰田汽车金融（中国                      业务种类：其他贷款\n：Y10041000H0001EHP2079494     ）有限公司\n                                                        五级分类认定日\n                余额          余额变化日期        五级分类                         逾期总额      逾期本金\n                                                           期\n 信息报告日期\n                        最近一次约定还          最近一次应还总        最近一次实际还       最近一次实还总   最近一次还款形\n               逾期月数       款日期               额             款日期            额         式\n\n                 0          2021-12-16      正常           2021-11-30      0         0\n  2021-12-16\n                 0          2021-12-16      0.35         2021-12-16     0.35     正常还款\n2.已结清账户编号                     授信机构：梅赛德斯-奔驰汽车金融 业务种类：固定资产贷款\n：Y10061000H0001EIP1537196     有限公司\n                                                        五级分类认定日\n                余额          余额变化日期        五级分类                         逾期总额      逾期本金\n                                                           期\n 信息报告日期\n                        最近一次约定还          最近一次应还总        最近一次实际还       最近一次实还总   最近一次还款形\n               逾期月数       款日期               额             款日期            额         式\n\n                 0          2021-10-22      正常           2021-10-22      0         0\n  2021-10-22\n                 0          2021-10-22      14.83        2021-10-22     14.83    正常还款\n3.已结清账户编号                 授信机构：平安国际融资租赁（天                         业务种类：其他贷款\n：M10251100H0002HX2020PAZL 津）有限公司\n200008308-ZL-01\n                                                        五级分类认定日\n                余额          余额变化日期        五级分类                         逾期总额      逾期本金\n                                                           期\n 信息报告日期\n                        最近一次约定还          最近一次应还总        最近一次实际还       最近一次实还总   最近一次还款形\n               逾期月数       款日期               额             款日期            额         式\n\n                 0          2021-08-16      正常               --          --        --\n  2021-08-16\n                 --             --           --          2021-08-16     2.37     正常还款\n4.已结清账户编号                 授信机构：平安国际融资租赁（天                         业务种类：其他贷款\n：M10251100H0002HX2020PAZL 津）有限公司\n200008312-ZL-01\n                                                        五级分类认定日\n                余额          余额变化日期        五级分类                         逾期总额      逾期本金\n                                                           期\n 信息报告日期\n                        最近一次约定还          最近一次应还总        最近一次实际还       最近一次实还总   最近一次还款形\n               逾期月数       款日期               额             款日期            额         式\n\n                 0          2021-08-16      正常               --          --        --\n  2021-08-16\n                 --             --           --          2021-08-16     2.37     正常还款\n\n（二）短期借款的历史表现\n1.未结清账户编号                   授信机构：南京银行股份有限公司                       业务种类：流动资金贷款\n：D10023010H0001041325112100 无锡城北支行\n000010\n                                                        五级分类认定日\n                余额          余额变化日期        五级分类                         逾期总额      逾期本金\n                                                           期\n 信息报告日期\n                        最近一次约定还          最近一次应还总        最近一次实际还       最近一次实还总   最近一次还款形\n               逾期月数       款日期               额             款日期            额         式\n\n                440         2025-11-21      正常           2025-11-28      0         0\n  2026-05-20\n                 0          2026-05-20      0.88         2026-05-20     0.88     正常还款\n\n  2026-04-20    440         2025-11-21      正常           2025-11-28      0         0\n\n\n                                         第 9 页/共 32 页\n\f               0      2026-04-20       0.91         2026-04-20     0.91     正常还款\n\n               440    2025-11-21       正常           2025-11-28      0         0\n 2026-03-20\n               0      2026-03-20       0.82         2026-03-20     0.82     正常还款\n\n               440    2025-11-21       正常           2025-11-28      0         0\n 2026-02-20\n               0      2026-02-20       0.91         2026-02-20     0.91     正常还款\n\n               440    2025-11-21       正常           2025-11-28      0         0\n 2026-01-20\n               0      2026-01-20       0.91         2026-01-20     0.91     正常还款\n\n               440    2025-11-21       正常           2025-11-28      0         0\n 2025-12-20\n               0      2025-12-20       0.85         2025-12-20     0.85     正常还款\n\n               440    2025-11-21       正常           2025-11-28      0         0\n 2025-11-28\n               0      2025-11-21         0          2025-11-21      0       正常还款\n2.未结清账户编号                   授信机构：中国农业银行股份有限                 业务种类：流动资金贷款\n：B10211000H0001320120250135 公司无锡分行\n943\n                                                   五级分类认定日\n               余额    余额变化日期          五级分类                         逾期总额      逾期本金\n                                                      期\n信息报告日期\n                     最近一次约定还       最近一次应还总         最近一次实际还       最近一次实还总   最近一次还款形\n              逾期月数     款日期            额              款日期            额         式\n\n               300    2025-12-25       正常           2025-12-25      0         0\n 2026-05-21\n               0      2026-05-21       0.60         2026-05-21     0.60     正常还款\n\n               300    2025-12-25       正常           2025-12-25      0         0\n 2026-04-21\n               0      2026-04-21       0.62         2026-04-21     0.62     正常还款\n\n               300    2025-12-25       正常           2025-12-25      0         0\n 2026-03-21\n               0      2026-03-21       0.56         2026-03-21     0.56     正常还款\n\n               300    2025-12-25       正常           2025-12-25      0         0\n 2026-02-21\n               0      2026-02-21       0.62         2026-02-21     0.62     正常还款\n\n               300    2025-12-25       正常           2025-12-25      0         0\n 2026-01-30\n               0      2026-01-21       0.54         2026-01-21     0.54     正常还款\n\n               300    2025-12-25       正常           2025-12-25      0         0\n 2025-12-25\n               0      2025-12-25         0          2025-12-25      0       正常还款\n3.未结清账户编号                   授信机构：交通银行股份有限公司                 业务种类：流动资金贷款\n：B10512900H0001322202510005 无锡分行\n1554\n                                                   五级分类认定日\n               余额    余额变化日期          五级分类                         逾期总额      逾期本金\n                                                      期\n信息报告日期\n                     最近一次约定还       最近一次应还总         最近一次实际还       最近一次实还总   最近一次还款形\n              逾期月数     款日期            额              款日期            额         式\n\n               200    2025-07-31       正常           2025-07-31      0         0\n 2026-05-21\n               0      2026-05-21       0.44         2026-05-21     0.44     正常还款\n\n               200    2025-07-31       正常           2025-07-31      0         0\n 2026-04-21\n               0      2026-04-21       0.46         2026-04-21     0.46     正常还款\n\n               200    2025-07-31       正常           2025-07-31      0         0\n 2026-03-23\n               0      2026-03-21       0.41         2026-03-23     0.41     正常还款\n\n 2026-02-24    200    2025-07-31       正常           2025-07-31      0         0\n\n\n\n                                   第 10 页/共 32 页\n\f               0      2026-02-21       0.46         2026-02-24     0.46     正常还款\n\n               200    2025-07-31       正常           2025-07-31      0         0\n 2026-01-21\n               0      2026-01-21       0.46         2026-01-21     0.46     正常还款\n\n               200    2025-07-31       正常           2025-07-31      0         0\n 2025-12-22\n               0      2025-12-21       0.44         2025-12-22     0.44     正常还款\n\n               200    2025-07-31       正常           2025-07-31      0         0\n 2025-11-21\n               0      2025-11-21       0.46         2025-11-21     0.46     正常还款\n\n               200    2025-07-31       正常           2025-07-31      0         0\n 2025-10-21\n               0      2025-10-21       0.44         2025-10-21     0.44     正常还款\n\n               200    2025-07-31       正常           2025-07-31      0         0\n 2025-09-22\n               0      2025-09-21       0.46         2025-09-22     0.46     正常还款\n\n               200    2025-07-31       正常           2025-07-31      0         0\n 2025-08-21\n               0      2025-08-21       0.31         2025-08-21     0.31     正常还款\n\n               200    2025-07-31       正常           2025-07-31      0         0\n 2025-07-31\n               0      2025-07-31         0          2025-07-31      0       正常还款\n4.未结清账户编号                   授信机构：中国农业银行股份有限                 业务种类：流动资金贷款\n：B10211000H0001320120250135 公司无锡分行\n927\n                                                   五级分类认定日\n               余额    余额变化日期          五级分类                         逾期总额      逾期本金\n                                                      期\n信息报告日期\n                     最近一次约定还       最近一次应还总         最近一次实际还       最近一次实还总   最近一次还款形\n              逾期月数     款日期            额              款日期            额         式\n\n               200    2025-12-25       正常           2025-12-25      0         0\n 2026-05-21\n               0      2026-05-21       0.40         2026-05-21     0.40     正常还款\n\n               200    2025-12-25       正常           2025-12-25      0         0\n 2026-04-21\n               0      2026-04-21       0.41         2026-04-21     0.41     正常还款\n\n               200    2025-12-25       正常           2025-12-25      0         0\n 2026-03-21\n               0      2026-03-21       0.37         2026-03-21     0.37     正常还款\n\n               200    2025-12-25       正常           2025-12-25      0         0\n 2026-02-21\n               0      2026-02-21       0.41         2026-02-21     0.41     正常还款\n\n               200    2025-12-25       正常           2025-12-25      0         0\n 2026-01-30\n               0      2026-01-21       0.36         2026-01-21     0.36     正常还款\n\n               200    2025-12-25       正常           2025-12-25      0         0\n 2025-12-25\n               0      2025-12-25         0          2025-12-25      0       正常还款\n5.未结清账户编号                  授信机构：江苏银行股份有限公司                  业务种类：流动资金贷款\n：D10123010H0001XW250527000 无锡科技支行\n000407\n                                                   五级分类认定日\n               余额    余额变化日期          五级分类                         逾期总额      逾期本金\n                                                      期\n信息报告日期\n                     最近一次约定还       最近一次应还总         最近一次实际还       最近一次实还总   最近一次还款形\n              逾期月数     款日期            额              款日期            额         式\n\n               100    2025-05-27       正常           2025-05-27      0         0\n 2026-05-21\n               0      2026-05-21       0.23         2026-05-21     0.23     正常还款\n\n 2026-04-21    100    2025-05-27       正常           2025-05-27      0         0\n\n\n\n                                   第 11 页/共 32 页\n\f               0       2026-04-21       0.23         2026-04-21     0.23      正常还款\n\n               100     2025-05-27       正常           2025-05-27      0          0\n 2026-03-21\n               0       2026</t>
+          <t>{"企业名称": "甲公司（通风机械）","中征码": "3202060003004372","统一社会信用代码": "91XXXXXXXXXXXXXXXX","查询机构": "中国农业银行股份有限公司江苏省分行","报告时间": "2026-05-25T15:02:46","报告编号": "NO.2026052515024689189187","页数": 32,"汇率_美元折人民币": "6.86","单位说明": "金额类数据项单位均为万元","method": "pdf_text_layer (deterministic)","full_text": "                          NO.2026052515024689189187\n\n\n\n\n        企业信用报告\n        （自主查询版）\n\n\n\n\n企业名称：         甲公司（通风机械）\n\n中征码：         3202060003004372\n\n统一社会信用代码： 91XXXXXXXXXXXXXXXX\n\n查询机构：        中国农业银行股份有限公司江苏省分行\n\n报告时间：        2026-05-25T15:02:46\n\n\n\n\n           第 1 页/共 32 页\n\f                         报告说明\n1．本报告由中国人民银行征信中心出具，依据截止报告时间征信系统记录的信息生成。除征信中心标注外，信息均由相关数据提\n供机构和信息主体提供，征信中心不保证其真实性和准确性，但承诺在信息汇总、加工、整合的全过程中保持客观、中立的地\n位。\n2．本报告所展示的基本信息来自征信系统对不同数据来源提供的同一个信息主体基本信息进行整合后的结果。\n3．本报告中信贷交易包括借贷交易和担保交易。\n4．本报告中借贷交易包括各种形式的贷款，也包括以各种其他名义融资但实质上是借贷的行为，即融资方负有明确还款责任的交\n易。常见的产品种类包括：贷款、贸易融资、票据贴现、保理、透支、融资租赁、回购、垫款、黄金证券借贷、公司信用债等。\n5．本报告中担保交易指第三人和债权人约定，当债务人不履行债务时，第三人按约定履行债务的行为。包括名义上没有担保合同\n约定但当债务人违约时、第三人实质上要代偿的行为。常见的产品种类包括：银行承兑汇票、信用证、银行保函、融资担保公司\n提供的担保服务，保险公司提供的信用保证保险服务。\n6．本报告中被追偿业务是指剩余本息处于催收状态（即债权人要求债务人尽快归还全部借款）的借贷交易。常见的产品种类包\n括：由资产管理公司处置的债务、垫款（含担保代偿）。\n7．本报告中的短期借款、中长期借款是指借贷交易中除被追偿业务、循环透支、贴现之外的业务，按照 “借款期限分类”划\n分，分别对应其中的短期、中期和长期。\n8．本报告中借贷交易的正常类是指除被追偿业务之外，五级分类为正常或者五级分类为“未分类”且逾期天数为0的业务；关注\n类是指除被追偿业务之外，五级分类为关注或者五级分类为“未分类”且逾期0至90天的业务；不良类是指除被追偿业务之外，五\n级分类为“次级”、“可疑”、“损失”、“违约”或者五级分类为“未分类”且逾期90天以上的业务。\n9．本报告中担保交易的正常类、关注类、不良类分别对应五级分类为正常、关注和后三类的业务。\n10．本报告中信息概要部分中的负债历史信息，其中负债是指由信贷交易所产生的债务；逾期总额、逾期本金是指除被追偿业务\n之外的借贷交易的逾期总额（含欠息）合计及逾期本金合计。\n11．本报告仅展示一定期限范围内的已结清信贷信息、非信贷信息、公共信息。\n12．如无特别说明，本报告中的金额类数据项单位均为万元。\n13．如无特别说明，本报告中的金额类汇总数据项均为人民币计价。外币折人民币的计算依据国家外汇管理局当月公布的各种货\n币对美元折算率表。\n14．如信息记录斜体展示，则说明信息主体对此条记录存在异议。\n15．数据提供机构说明是报数机构对报告中的信息记录或对信息主体所作的补充说明。\n16．征信中心说明是征信中心对报告中的信息记录或对信息主体所作的说明。\n17．信息主体声明是信息主体对报数机构提供的信息记录所作的简要说明。\n18．信息主体有权对本报告中的内容提出异议。如有异议，可联系报数机构，也可到当地信用报告查询网点（具体地址可查询征\n信中心网站www.pbccrc.org.cn）提出异议申请。\n19．本报告仅向信息主体提供，不为金融机构授信管理目的使用，请妥善保管。因保管不当造成信息泄露的，征信中心不承担相\n关责任。\n20．更多咨询，请致电全国客户服务热线400-810-8866。\n汇率（美元折人民币）：6.86        有效期：2026-05\n\n\n\n\n                          第 2 页/共 32 页\n\f                                                    身份标识\n\n           企业名称                        甲公司（通风机械）\n\n            中征码                        3202060003004372\n\n      统一社会信用代码                         91XXXXXXXXXXXXXXXX\n\n       组织机构代码                          MA1MDD2LX\n\n           工商注册号                       91XXXXXXXXXXXXXXXX\n\n     纳税人识别号（国税）                        91XXXXXXXXXXXXXXXX\n\n     纳税人识别号（地税）                        91XXXXXXXXXXXXXXXX\n\n\n\n\n                                                    信息概要\n\n                                                                       当前有未结清信贷                     首次有相关还款\n 首次有信贷交易的年份                    发生信贷交易的机构数                               交易的机构数                       责任的年份\n\n           2019                             10                               5                           2022\n\n\n\n                        借贷交易                                                               担保交易\n\n余额                                                    1240        余额                                                      180\n\n其中：被追偿余额                                                  0       其中：关注类余额                                                 0\n\n     关注类余额                                                0            不良类余额                                               0\n\n     不良类余额                                                0\n\n\n\n 非信贷交易账户数                欠税记录条数                    民事判决记录条数                      强制执行记录条数            行政处罚记录条数\n\n       0                           0                          0                        0                        0\n\n\n\n 未结清信贷及授信信息概要\n                       正常类                        关注类                            不良类                      合计\n\n              账户数            余额             账户数           余额            账户数            余额           账户数             余额\n\n短期借款              5          1240             0               0          0                 0         5              1240\n\n 合计               5          1240             0               0          0                 0         5              1240\n\n\n\n                       正常类                        关注类                            不良类                      合计\n\n              账户数            余额             账户数           余额            账户数            余额           账户数             余额\n\n银行承兑汇             14         180              0               0          0                 0        14              180\n  票\n\n 合计               14         180              0               0          0                 0        14              180\n\n\n\n 相关还款责任信息概要\n                                       被追偿业务                                           其他借贷交易\n     责任类型\n                        还款责任                                      还款责任                              关注类余            不良类余\n                                        账户数        余额                        账户数               余额\n                         金额                                        金额                                 额              额\n\n\n                                                     第 3 页/共 32 页\n\f     个人信贷交易共同     --           0          0         --        1        17.30      0          0\n     还款人/共同债务人\n\n        合计        0            0          0         0         1        17.30      0          0\n\n\n\n     已结清信贷信息概要\n                  正常类账户数                  关注类账户数              不良类账户数                   合计\n\n      中长期借款             4                      0                   0                   4\n\n       短期借款             17                     0                   0                   17\n\n        合计              21                     0                   0                   21\n\n\n\n                  正常类账户数                  关注类账户数              不良类账户数                   合计\n\n      银行承兑汇票            181                    0                   0                   181\n\n        合计              181                    0                   0                   181\n\n\n\n\n                                          基本信息\n\n     基本概况信息\n                                                                          中国农业银行股份有限公司无\n        经济类型                  有限责任(公司)                   信息来源机构                锡分行\n\n                                                                          中国农业银行股份有限公司无\n       组织机构类型                      企业                    信息来源机构                锡分行\n\n                                                                          中国农业银行股份有限公司无\n        企业规模                   小型企业                      信息来源机构                锡分行\n\n                                                                          中国农业银行股份有限公司无\n        所属行业                 风机、风扇制造                     信息来源机构                锡分行\n\n                                                                          中国农业银行股份有限公司无\n        成立年份                       2015                  信息来源机构                锡分行\n\n                                                                          中国农业银行股份有限公司无\n     登记证书有效截止日期                    长期                    信息来源机构                锡分行\n\n                       无锡市惠山区堰桥街道堰锦路                                      中国农业银行股份有限公司无\n        登记地址                                             信息来源机构\n                             22                                                锡分行\n\n                       无锡市惠山区堰桥街道堰锦路                                      南京银行股份有限公司无锡城\n       办公/经营地址                                           信息来源机构\n                             22                                                北支行\n\n                                                                          中国农业银行股份有限公司无\n        存续状态                   正常营业                      信息来源机构                锡分行\n--\n\n\n\n     注册资本及主要出资人信息                                                       注册资本折人民币合计 1000万元\n\n        类型             出资方                身份标识类型              身份标识号码                  出资比例\n\n        股东             杨春平                    身份证          320125197904075814         51%\n\n        股东             黄燕红                    身份证          32028319890903322X         49%\n\n 信息来源机构：中国农业银行股份有限公司无锡分行                                                        更新日期：2026-01-30\n\n\n\n     主要组成人员信息\n\n\n\n                                          第 4 页/共 32 页\n\f         职位                  姓名                            证件类型                    证件号码\n\n法定代表人/非法人组织负责                杨春平                           身份证              320125197904075814\n      人\n\n信息来源机构：江苏银行股份有限公司无锡科技支行                                                        更新日期：2025-04-28\n\n\n\n 实际控制人\n              名称                           身份标识类型                          身份标识号码\n\n           杨春平                               身份证                        320125197904075814\n\n信息来源机构：中国农业银行股份有限公司无锡分行                                                        更新日期：2026-01-30\n\n\n\n\n                                   信贷记录明细\n\n 未结清信贷\n 短期借款                                                                                           共5笔\n           授信机构       业务种类         开立日期             到期日           币种       借款金额            发放形式\n\n                                                                                         最近一次还款\n账户编        担保方式        余额          五级分类            逾期总额          逾期本金      逾期月数            日期\n 号\n                     最近一次还款                       授信协议编\n         最近一次还款总额              特定交易提示                            历史表现             信息报告日期\n                       形式                           号\n\nD10023   南京银行股份有限    流动资金贷款       2025-11-21      2026-11-19     人民币元        440          无还本续贷\n010H00   公司无锡城北支行\n010413\n251121        保证       440          正常                0            0          0           2026-05-20\n000000\n  10          0.88    正常还款            --              --          见附件              2026-05-20\n\n         中国农业银行股份\nB10211               流动资金贷款       2025-12-25      2026-12-15     人民币元        300          无还本续贷\n         有限公司无锡分行\n000H00\n013201        保证       300          正常                0            0          0           2026-05-21\n202501\n 35943\n              0.60    正常还款            --              --          见附件              2026-05-21\n\n         交通银行股份有限    流动资金贷款       2025-07-31      2026-07-30     人民币元        200                新增\n          公司无锡分行\nB10512\n900H00        保证       200          正常                0            0          0           2026-05-21\n013222\n025100                                           B10512900H\n051554                                           0001BL1563\n              0.44    正常还款            --                          见附件              2026-05-21\n                                                 22250703944\n                                                      3\n\n         中国农业银行股份\nB10211               流动资金贷款       2025-12-25      2026-12-15     人民币元        200          无还本续贷\n         有限公司无锡分行\n000H00\n013201        保证       200          正常                0            0          0           2026-05-21\n202501\n 35927\n              0.40    正常还款            --              --          见附件              2026-05-21\n\n         江苏银行股份有限    流动资金贷款       2025-05-27      2026-05-26     人民币元        100                新增\n         公司无锡科技支行\nD10123\n010H00        保证       100          正常                0            0          0           2026-05-21\n01XW2\n505270\n000004                                           D10123010H\n  07                                             0001BC2025\n              0.23    正常还款            --                          见附件              2026-05-21\n                                                 0522001197\n                                                     DK\n\n\n\n\n                                           第 5 页/共 32 页\n\f 银行承兑汇票和信用证                                                                                  共 14 笔\n     授信机构                     业务种类         五级分类                     账户数                余额\n\n交通银行股份有限公司               银行承兑汇票              正常                          14            180\n\n\n\n  已结清信贷\n 中长期借款                                                                                        共4笔\n                 授信机构            业务种类      开立日期              到期日                 币种    借款金额\n  账户编号\n                 关闭日期            五级分类       最后一次还款日期                 最后一次还款形式          历史表现\n\n                 丰田汽车金融\n                （中国）有限公          其他贷款      2019-12-16       2021-12-16          人民币元     8.50\nY10041000H00        司\n01EHP2079494\n                 2021-12-16          正常        2021-12-16                     正常还款      见附件\n\n                梅赛德斯-奔驰\n                汽车金融有限公         固定资产贷款     2020-04-24       2021-10-24          人民币元     14.82\nY10061000H00       司\n01EIP1537196\n                 2021-10-22          正常        2021-10-22                     正常还款      见附件\n\n                平安国际融资租\nM10251100H0     赁（天津）有限          其他贷款      2020-05-25       2021-10-25          人民币元     20.25\n002HX2020PA        公司\nZL200008308-\n   ZL-01\n                 2021-08-16          正常        2021-08-16                     正常还款      见附件\n\n                平安国际融资租\nM10251100H0     赁（天津）有限          其他贷款      2020-05-15       2021-10-15          人民币元     19.80\n002HX2020PA        公司\nZL200008312-\n   ZL-01\n                 2021-08-16          正常        2021-08-16                     正常还款      见附件\n\n\n\n 短期借款                                                                                        共 17 笔\n                 授信机构            业务种类      开立日期              到期日                 币种    借款金额\n  账户编号\n                 关闭日期            五级分类       最后一次还款日期                 最后一次还款形式          历史表现\n\n                中国农业银行股\nB10211000H00    份有限公司无锡         流动资金贷款     2025-08-06       2026-08-04          人民币元         300\n0132012025008      分行\n     6673\n                 2025-12-25          正常        2025-12-25                     正常还款      见附件\n\n                中国农业银行股\nB10211000H00    份有限公司无锡         流动资金贷款     2025-08-08       2026-08-03          人民币元         200\n0132012025008      分行\n     7282\n                 2025-12-25          正常        2025-12-25                     正常还款      见附件\n\n                南京银行股份有\nD10023010H00    限公司无锡城北         流动资金贷款     2024-12-10       2025-12-08          人民币元         440\n0104132412100      支行\n   0000005\n                 2025-11-21          正常        2025-11-21                     正常还款      见附件\n\n                中国农业银行股\nB10211000H00    份有限公司无锡         流动资金贷款     2024-08-20       2025-08-19          人民币元         200\n0132012024009      分行\n     3062\n                 2025-08-08          正常        2025-08-08                     正常还款      见附件\n\n                中国农业银行股\nB10211000H00    份有限公司无锡         流动资金贷款     2024-08-20       2025-08-18          人民币元         300\n0132012024009      分行\n     2579\n                 2025-08-06          正常        2025-08-06                     正常还款      见附件\n\n\n\n\n                                          第 6 页/共 32 页\n\f                交通银行股份有\nB10512900H00                  流动资金贷款        2024-08-13       2025-08-12     人民币元    300\n                限公司无锡分行\n0132220240000\n    70638\n                 2025-07-31     正常              2025-07-31                正常还款     见附件\n\n                交通银行股份有\nB10512900H00                  流动资金贷款        2024-08-08       2025-08-07     人民币元    200\n                限公司无锡分行\n0132220240000\n    70095\n                 2025-07-31     正常              2025-07-31                正常还款     见附件\n\n                中国农业银行股\nB10211000H00    份有限公司无锡       流动资金贷款        2023-09-21       2024-09-20     人民币元    200\n0132012023010      分行\n     5691\n                 2024-08-20     正常              2024-08-20                正常还款     见附件\n\n                中国农业银行股\nB10211000H00    份有限公司无锡       流动资金贷款        2023-09-20       2024-09-18     人民币元    300\n0132012023010      分行\n     4308\n                 2024-08-19     正常              2024-08-19                正常还款     见附件\n\n                交通银行股份有\nB10512900H00                  流动资金贷款        2023-08-31       2024-08-31     人民币元    300\n                限公司无锡分行\n0132220230000\n    34697\n                 2024-08-12     正常              2024-08-12                正常还款     见附件\n\n                交通银行股份有\nB10512900H00                  流动资金贷款        2023-08-31       2024-08-31     人民币元    200\n                限公司无锡分行\n0132220230000\n    34729\n                 2024-08-05     正常              2024-08-05                正常还款     见附件\n\n                中国农业银行股\nB10211000H00    份有限公司无锡       流动资金贷款        2022-09-23       2023-09-22     人民币元    500\n0132012022007      分行\n     4966\n                 2023-09-21     正常              2023-09-21                正常还款     见附件\n\n                中国农业银行股\nB10211000H00    份有限公司无锡       流动资金贷款        2021-11-10       2022-11-09     人民币元    200\n0132012021008      分行\n     5887\n                 2022-09-23     正常              2022-09-23                正常还款     见附件\n\n                中国农业银行股\nB10211000H00    份有限公司无锡       流动资金贷款        2021-11-12       2022-11-11     人民币元    300\n0132012021008      分行\n     6662\n                 2022-09-23     正常              2022-09-23                正常还款     见附件\n\n                中国农业银行股\nB10211000H00    份有限公司无锡       流动资金贷款        2021-03-02       2022-03-01     人民币元    300\n0132012021001      分行\n     5429\n                 2021-11-12     正常              2021-11-12                正常还款     见附件\n\n                中国农业银行股\nB10211000H00    份有限公司无锡       流动资金贷款        2021-03-01       2022-02-21     人民币元    200\n0132012021001      分行\n     4919\n                 2021-11-10     正常              2021-11-10                正常还款     见附件\n\n                中国农业银行股\nB10211000H00    份有限公司无锡       流动资金贷款        2020-03-23       2021-03-12     人民币元    300\n0132012020001     惠山支行\n     7424\n                 2021-03-02     正常              2021-03-02                正常还款     见附件\n\n\n\n 银行承兑汇票和信用证                                                                        共 181 笔\n         授信机构                        业务种类                    五级分类          账户数     垫款标志\n\n    浙商银行股份有限公司                   银行承兑汇票                       正常            107     否\n\n    江苏银行股份有限公司                   银行承兑汇票                       正常            34      否\n\n江苏常熟农村商业银行股份有限                   银行承兑汇票                       正常            21      否\n      公司\n\n\n                                        第 7 页/共 32 页\n\f   交通银行股份有限公司                 银行承兑汇票                        正常                12               否\n\n  中国农业银行股份有限公司                银行承兑汇票                        正常                7                否\n\n\n\n 相关还款责任\n 为其他借款人承担的相关还款责任\n除贴现外的其他业务                                                                                       共1笔\n                    保证合同             还款责任       授信机构/                 开立日期/\n           责任类型              币种                              业务种类                   到期日         币种\n                     编号               金额        债权机构                  接收日期\n账户编号\n           借款金额/                                            逾期月数/     剩余还款\n                     余额     五级分类     逾期总额       逾期本金                                  信息报告日期\n           信用额度                                             还款状态       月数\n\nD1005584   个人信贷                                 深圳前海\n0H0001D    交易共同                                 微众银行         个人汽车     2025-02-     2030-02-\n                     --     人民币元        --                                                     人民币元\n18300640   还款人/共                                股份有限         消费贷款        10           10\n10926946   同债务人                                  公司\n72123250\n21002649\n  86440     22.42   17.30    正常         0          0              N      --            2026-05-10\n\n\n\n\n                                    公共记录明细\n\n 获得许可记录\n    许可部门            许可类型           许可日期                 截止日期                       许可内容\n\n无锡市惠山区行政             登记            2024-10-21           2099-12-31                  登字\n   审批局\n\n无锡市惠山区行政             登记            2024-09-29           2099-12-31                  登字\n   审批局\n\n                                                                      设备类别:第二类压力容器，产品名\n                                                                      称:储气罐，出厂编号:FP2004D387-\n无锡市惠山区市场             普通            2022-11-11           2099-12-31     2，单位内编号:R-01，设备代码\n  监督管理局                                                               :215033025202000259，设备注册\n                                                                        代码:21503202062022110016\n\n无锡市惠山区市场             登记            2021-05-24           2099-12-31                 变更登记\n  监督管理局\n\n无锡市惠山区市场             登记            2015-12-28           2099-12-31                 公司变更\n  监督管理局\n\n\n\n 获得认证记录\n           认证部门                   认证类型                    认证日期          截止日期                  认证内容\n\n                                                                                        2022年度纳税信\n       国家税务总局                纳税信用A级纳税人                       --        2028-12-31        用A级纳税人\n\n\n\n\n                                         第 8 页/共 32 页\n\f附件1：信用记录补充信息\n\n一、信贷记录\n（一）中长期借款的历史表现\n1.已结清账户编号                     授信机构：丰田汽车金融（中国                      业务种类：其他贷款\n：Y10041000H0001EHP2079494     ）有限公司\n                                                        五级分类认定日\n                余额          余额变化日期        五级分类                         逾期总额      逾期本金\n                                                           期\n 信息报告日期\n                        最近一次约定还          最近一次应还总        最近一次实际还       最近一次实还总   最近一次还款形\n               逾期月数       款日期               额             款日期            额         式\n\n                 0          2021-12-16      正常           2021-11-30      0         0\n  2021-12-16\n                 0          2021-12-16      0.35         2021-12-16     0.35     正常还款\n2.已结清账户编号                     授信机构：梅赛德斯-奔驰汽车金融 业务种类：固定资产贷款\n：Y10061000H0001EIP1537196     有限公司\n                                                        五级分类认定日\n                余额          余额变化日期        五级分类                         逾期总额      逾期本金\n                                                           期\n 信息报告日期\n                        最近一次约定还          最近一次应还总        最近一次实际还       最近一次实还总   最近一次还款形\n               逾期月数       款日期               额             款日期            额         式\n\n                 0          2021-10-22      正常           2021-10-22      0         0\n  2021-10-22\n                 0          2021-10-22      14.83        2021-10-22     14.83    正常还款\n3.已结清账户编号                 授信机构：平安国际融资租赁（天                         业务种类：其他贷款\n：M10251100H0002HX2020PAZL 津）有限公司\n200008308-ZL-01\n                                                        五级分类认定日\n                余额          余额变化日期        五级分类                         逾期总额      逾期本金\n                                                           期\n 信息报告日期\n                        最近一次约定还          最近一次应还总        最近一次实际还       最近一次实还总   最近一次还款形\n               逾期月数       款日期               额             款日期            额         式\n\n                 0          2021-08-16      正常               --          --        --\n  2021-08-16\n                 --             --           --          2021-08-16     2.37     正常还款\n4.已结清账户编号                 授信机构：平安国际融资租赁（天                         业务种类：其他贷款\n：M10251100H0002HX2020PAZL 津）有限公司\n200008312-ZL-01\n                                                        五级分类认定日\n                余额          余额变化日期        五级分类                         逾期总额      逾期本金\n                                                           期\n 信息报告日期\n                        最近一次约定还          最近一次应还总        最近一次实际还       最近一次实还总   最近一次还款形\n               逾期月数       款日期               额             款日期            额         式\n\n                 0          2021-08-16      正常               --          --        --\n  2021-08-16\n                 --             --           --          2021-08-16     2.37     正常还款\n\n（二）短期借款的历史表现\n1.未结清账户编号                   授信机构：南京银行股份有限公司                       业务种类：流动资金贷款\n：D10023010H0001041325112100 无锡城北支行\n000010\n                                                        五级分类认定日\n                余额          余额变化日期        五级分类                         逾期总额      逾期本金\n                                                           期\n 信息报告日期\n                        最近一次约定还          最近一次应还总        最近一次实际还       最近一次实还总   最近一次还款形\n               逾期月数       款日期               额             款日期            额         式\n\n                440         2025-11-21      正常           2025-11-28      0         0\n  2026-05-20\n                 0          2026-05-20      0.88         2026-05-20     0.88     正常还款\n\n  2026-04-20    440         2025-11-21      正常           2025-11-28      0         0\n\n\n                                         第 9 页/共 32 页\n\f               0      2026-04-20       0.91         2026-04-20     0.91     正常还款\n\n               440    2025-11-21       正常           2025-11-28      0         0\n 2026-03-20\n               0      2026-03-20       0.82         2026-03-20     0.82     正常还款\n\n               440    2025-11-21       正常           2025-11-28      0         0\n 2026-02-20\n               0      2026-02-20       0.91         2026-02-20     0.91     正常还款\n\n               440    2025-11-21       正常           2025-11-28      0         0\n 2026-01-20\n               0      2026-01-20       0.91         2026-01-20     0.91     正常还款\n\n               440    2025-11-21       正常           2025-11-28      0         0\n 2025-12-20\n               0      2025-12-20       0.85         2025-12-20     0.85     正常还款\n\n               440    2025-11-21       正常           2025-11-28      0         0\n 2025-11-28\n               0      2025-11-21         0          2025-11-21      0       正常还款\n2.未结清账户编号                   授信机构：中国农业银行股份有限                 业务种类：流动资金贷款\n：B10211000H0001320120250135 公司无锡分行\n943\n                                                   五级分类认定日\n               余额    余额变化日期          五级分类                         逾期总额      逾期本金\n                                                      期\n信息报告日期\n                     最近一次约定还       最近一次应还总         最近一次实际还       最近一次实还总   最近一次还款形\n              逾期月数     款日期            额              款日期            额         式\n\n               300    2025-12-25       正常           2025-12-25      0         0\n 2026-05-21\n               0      2026-05-21       0.60         2026-05-21     0.60     正常还款\n\n               300    2025-12-25       正常           2025-12-25      0         0\n 2026-04-21\n               0      2026-04-21       0.62         2026-04-21     0.62     正常还款\n\n               300    2025-12-25       正常           2025-12-25      0         0\n 2026-03-21\n               0      2026-03-21       0.56         2026-03-21     0.56     正常还款\n\n               300    2025-12-25       正常           2025-12-25      0         0\n 2026-02-21\n               0      2026-02-21       0.62         2026-02-21     0.62     正常还款\n\n               300    2025-12-25       正常           2025-12-25      0         0\n 2026-01-30\n               0      2026-01-21       0.54         2026-01-21     0.54     正常还款\n\n               300    2025-12-25       正常           2025-12-25      0         0\n 2025-12-25\n               0      2025-12-25         0          2025-12-25      0       正常还款\n3.未结清账户编号                   授信机构：交通银行股份有限公司                 业务种类：流动资金贷款\n：B10512900H0001322202510005 无锡分行\n1554\n                                                   五级分类认定日\n               余额    余额变化日期          五级分类                         逾期总额      逾期本金\n                                                      期\n信息报告日期\n                     最近一次约定还       最近一次应还总         最近一次实际还       最近一次实还总   最近一次还款形\n              逾期月数     款日期            额              款日期            额         式\n\n               200    2025-07-31       正常           2025-07-31      0         0\n 2026-05-21\n               0      2026-05-21       0.44         2026-05-21     0.44     正常还款\n\n               200    2025-07-31       正常           2025-07-31      0         0\n 2026-04-21\n               0      2026-04-21       0.46         2026-04-21     0.46     正常还款\n\n               200    2025-07-31       正常           2025-07-31      0         0\n 2026-03-23\n               0      2026-03-21       0.41         2026-03-23     0.41     正常还款\n\n 2026-02-24    200    2025-07-31       正常           2025-07-31      0         0\n\n\n\n                                   第 10 页/共 32 页\n\f               0      2026-02-21       0.46         2026-02-24     0.46     正常还款\n\n               200    2025-07-31       正常           2025-07-31      0         0\n 2026-01-21\n               0      2026-01-21       0.46         2026-01-21     0.46     正常还款\n\n               200    2025-07-31       正常           2025-07-31      0         0\n 2025-12-22\n               0      2025-12-21       0.44         2025-12-22     0.44     正常还款\n\n               200    2025-07-31       正常           2025-07-31      0         0\n 2025-11-21\n               0      2025-11-21       0.46         2025-11-21     0.46     正常还款\n\n               200    2025-07-31       正常           2025-07-31      0         0\n 2025-10-21\n               0      2025-10-21       0.44         2025-10-21     0.44     正常还款\n\n               200    2025-07-31       正常           2025-07-31      0         0\n 2025-09-22\n               0      2025-09-21       0.46         2025-09-22     0.46     正常还款\n\n               200    2025-07-31       正常           2025-07-31      0         0\n 2025-08-21\n               0      2025-08-21       0.31         2025-08-21     0.31     正常还款\n\n               200    2025-07-31       正常           2025-07-31      0         0\n 2025-07-31\n               0      2025-07-31         0          2025-07-31      0       正常还款\n4.未结清账户编号                   授信机构：中国农业银行股份有限                 业务种类：流动资金贷款\n：B10211000H0001320120250135 公司无锡分行\n927\n                                                   五级分类认定日\n               余额    余额变化日期          五级分类                         逾期总额      逾期本金\n                                                      期\n信息报告日期\n                     最近一次约定还       最近一次应还总         最近一次实际还       最近一次实还总   最近一次还款形\n              逾期月数     款日期            额              款日期            额         式\n\n               200    2025-12-25       正常           2025-12-25      0         0\n 2026-05-21\n               0      2026-05-21       0.40         2026-05-21     0.40     正常还款\n\n               200    2025-12-25       正常           2025-12-25      0         0\n 2026-04-21\n               0      2026-04-21       0.41         2026-04-21     0.41     正常还款\n\n               200    2025-12-25       正常           2025-12-25      0         0\n 2026-03-21\n               0      2026-03-21       0.37         2026-03-21     0.37     正常还款\n\n               200    2025-12-25       正常           2025-12-25      0         0\n 2026-02-21\n               0      2026-02-21       0.41         2026-02-21     0.41     正常还款\n\n               200    2025-12-25       正常           2025-12-25      0         0\n 2026-01-30\n               0      2026-01-21       0.36         2026-01-21     0.36     正常还款\n\n               200    2025-12-25       正常           2025-12-25      0         0\n 2025-12-25\n               0      2025-12-25         0          2025-12-25      0       正常还款\n5.未结清账户编号                  授信机构：江苏银行股份有限公司                  业务种类：流动资金贷款\n：D10123010H0001XW250527000 无锡科技支行\n000407\n                                                   五级分类认定日\n               余额    余额变化日期          五级分类                         逾期总额      逾期本金\n                                                      期\n信息报告日期\n                     最近一次约定还       最近一次应还总         最近一次实际还       最近一次实还总   最近一次还款形\n              逾期月数     款日期            额              款日期            额         式\n\n               100    2025-05-27       正常           2025-05-27      0         0\n 2026-05-21\n               0      2026-05-21       0.23         2026-05-21     0.23     正常还款\n\n 2026-04-21    100    2025-05-27       正常           2025-05-27      0         0\n\n\n\n                                   第 11 页/共 32 页\n\f               0       2026-04-21       0.23         2026-04-21     0.23      正常还款\n\n               100     2025-05-27       正常           2025-05-27      0          0\n 2026-03-21\n               0       2026</t>
         </is>
       </c>
       <c r="V125" s="4" t="inlineStr"/>
